--- a/data/trans_orig/IP16A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A02-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>25619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>26537</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>15706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23508</t>
+          <t>23417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36163</t>
+          <t>35873</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47955</t>
+          <t>47520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,28%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14530</t>
+          <t>14819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25170</t>
+          <t>24885</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23989</t>
+          <t>23595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>37049</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26543</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35310</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26776</t>
+          <t>26487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>44932</t>
+          <t>45903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58963</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12990</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20881</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30781</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12174</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19589</t>
+          <t>19457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23824</t>
+          <t>23676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>29569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41997</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7046</t>
+          <t>7402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>15557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19887</t>
+          <t>20515</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33589</t>
+          <t>32792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9814</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18930</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28661</t>
+          <t>28610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>31702</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>44839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>69,52%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32457</t>
+          <t>33713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49838</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>50907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68950</t>
+          <t>68801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87583</t>
+          <t>89310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113508</t>
+          <t>114590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>75467</t>
+          <t>74080</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>92848</t>
+          <t>91592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>75118</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>93752</t>
+          <t>93012</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>155716</t>
+          <t>154634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181641</t>
+          <t>179914</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>10439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21817</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12018</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39659</t>
+          <t>40053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30224</t>
+          <t>30603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27225</t>
+          <t>27328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40729</t>
+          <t>40335</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>54648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>67,98%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19228</t>
+          <t>19367</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30802</t>
+          <t>30871</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>12826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>24028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51847</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,87%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>21512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33155</t>
+          <t>33016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>28166</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39614</t>
+          <t>39368</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>52730</t>
+          <t>53472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68904</t>
+          <t>70029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,96%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12284</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22944</t>
+          <t>23255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14790</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26135</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45923</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,51%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>20174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31145</t>
+          <t>30443</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25093</t>
+          <t>25384</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36438</t>
+          <t>36633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49466</t>
+          <t>48734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>64290</t>
+          <t>63678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26622</t>
+          <t>26700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>14085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25709</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>31781</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>49188</t>
+          <t>48693</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>35832</t>
+          <t>35260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24232</t>
+          <t>24141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36041</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>51537</t>
+          <t>52032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68170</t>
+          <t>68944</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,17%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67876</t>
+          <t>67251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89891</t>
+          <t>90680</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64620</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86300</t>
+          <t>87054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138008</t>
+          <t>138640</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171072</t>
+          <t>172841</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97746</t>
+          <t>96957</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119761</t>
+          <t>120386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>106410</t>
+          <t>105656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128090</t>
+          <t>128646</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209275</t>
+          <t>207506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242339</t>
+          <t>241707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>15923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>24309</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>24895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16185</t>
+          <t>16307</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24464</t>
+          <t>24876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35039</t>
+          <t>35734</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47121</t>
+          <t>47333</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,83%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14471</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>31559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46209</t>
+          <t>47529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>28370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39338</t>
+          <t>39571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23897</t>
+          <t>23996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35290</t>
+          <t>35250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>55650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>72076</t>
+          <t>71620</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18673</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18776</t>
+          <t>19069</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22121</t>
+          <t>22198</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>34237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,62%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15275</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24206</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22030</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31812</t>
+          <t>32086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44202</t>
+          <t>44125</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,53%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>24407</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>49,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24313</t>
+          <t>24760</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39278</t>
+          <t>39425</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,61%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>19423</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30495</t>
+          <t>30685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19402</t>
+          <t>18907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28726</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41822</t>
+          <t>41675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56787</t>
+          <t>56340</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53571</t>
+          <t>53029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73725</t>
+          <t>73357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>44835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63813</t>
+          <t>63534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104160</t>
+          <t>103391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>132584</t>
+          <t>131952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89534</t>
+          <t>89902</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109688</t>
+          <t>110230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>83572</t>
+          <t>83851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102155</t>
+          <t>102550</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178061</t>
+          <t>178693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>206485</t>
+          <t>207254</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>14512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12626</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24232</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>11329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19323</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>15448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23425</t>
+          <t>23552</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29269</t>
+          <t>29655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40850</t>
+          <t>40818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24622</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22655</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36805</t>
+          <t>36150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37255</t>
+          <t>37589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57500</t>
+          <t>57301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>20379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33498</t>
+          <t>33560</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27004</t>
+          <t>27659</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41154</t>
+          <t>41919</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50551</t>
+          <t>50750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70796</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47553</t>
+          <t>48174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18760</t>
+          <t>19199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34235</t>
+          <t>34248</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74495</t>
+          <t>74195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29518</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66914</t>
+          <t>67168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38163</t>
+          <t>37724</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59499</t>
+          <t>59799</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102488</t>
+          <t>106431</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18808</t>
+          <t>18738</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11399</t>
+          <t>11104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21310</t>
+          <t>21095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24048</t>
+          <t>23542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37553</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20816</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22410</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26817</t>
+          <t>27022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40322</t>
+          <t>40828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43225</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>89860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68245</t>
+          <t>67131</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92357</t>
+          <t>91778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116988</t>
+          <t>113536</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172684</t>
+          <t>171925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,77%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>87855</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134490</t>
+          <t>133859</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89844</t>
+          <t>90423</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113956</t>
+          <t>115070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187232</t>
+          <t>187991</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>242928</t>
+          <t>246380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A02-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8662</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4989</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13272</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,28%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10598</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6281</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15293</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6368</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>15012</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,29%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>19,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8662</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5257</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12968</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>30,21%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25619</t>
+          <t>25675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20012</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15402</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23685</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,72%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>82,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>22220</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17525</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26537</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17806</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26450</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,71%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>53,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>80,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20012</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15706</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23417</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>69,79%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35873</t>
+          <t>35817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47520</t>
+          <t>47198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32818</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>28674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19929</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15141</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25784</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>36,66%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>62,42%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10553</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6839</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15489</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6770</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>15554</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>25,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,19%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19929</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14819</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24885</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>48,25%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23595</t>
+          <t>23969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37049</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>45,62%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21377</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15522</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26165</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>51,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>37,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>63,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>31094</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>26158</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>34808</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>26093</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>34877</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>74,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>21377</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>16421</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>26487</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>51,75%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45903</t>
+          <t>45109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59357</t>
+          <t>58983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41306</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41647</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41306</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15716</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11308</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>20669</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8925</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5707</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13030</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5255</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>12669</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>35,47%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,78%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>15716</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11447</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18209</t>
+          <t>18446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>30727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>19407</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14454</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23815</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>67,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>16239</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12134</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>19457</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12495</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>19909</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>64,53%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>19407</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>14299</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23676</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>55,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>29569</t>
+          <t>29559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>41840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35123</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>25164</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15037</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10713</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20833</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>38,74%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>53,67%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>11220</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7402</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15557</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>6870</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15627</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>43,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15037</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10207</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>20515</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>38,74%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>20348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32792</t>
+          <t>32831</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23780</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17984</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28104</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>61,26%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>46,33%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,4%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>14457</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>10120</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>10050</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18807</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>56,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>39,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23780</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>18302</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28610</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>61,26%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31702</t>
+          <t>31663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44839</t>
+          <t>44146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>68,45%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38817</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>25677</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38817</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>59343</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>50277</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>68940</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>41,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>34,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,9%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>41295</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33713</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>51225</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32833</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>50167</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,96%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>40,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>59343</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>50907</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>68801</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89310</t>
+          <t>89012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114590</t>
+          <t>113480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,15%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>84576</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>74979</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>93642</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>58,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52,1%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>84010</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>74080</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>91592</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>75138</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>92472</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>67,04%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>59,12%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>73,1%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>84576</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>75118</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>93012</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>58,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>154634</t>
+          <t>155744</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>179914</t>
+          <t>180212</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17005</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12226</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22213</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>31,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15547</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10439</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21434</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10632</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21309</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,88%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,44%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,22%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17005</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12018</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22907</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>43,22%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25740</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40053</t>
+          <t>39873</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,6%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22341</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>17133</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27120</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>56,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>43,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>68,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25495</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>19608</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30603</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>19733</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>30410</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>62,12%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>47,78%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22341</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16439</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>27328</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>56,78%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40335</t>
+          <t>40515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54648</t>
+          <t>55438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -2901,52 +2901,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39346</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>41042</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>39346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18301</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13069</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24168</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>24842</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19367</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>30871</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>19169</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>30516</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>47,42%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>36,97%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>58,93%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>18301</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>12826</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>24028</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34548</t>
+          <t>35032</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>51528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33893</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28026</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>27541</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21512</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33016</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21867</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>33214</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>52,58%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>41,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>63,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>33893</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>28166</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>39368</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>53472</t>
+          <t>53049</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70029</t>
+          <t>69545</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,5%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>52194</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>52194</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>52194</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>52383</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>52383</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>52383</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>52194</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>52194</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>52194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20340</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15218</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25953</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>29,71%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>50,66%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>17504</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12986</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23255</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>12953</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>22790</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>20340</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>14595</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25844</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30979</t>
+          <t>30767</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45923</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30888</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25275</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36010</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>60,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>49,34%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70,29%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>25925</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20174</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30443</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20639</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30476</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>59,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>70,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30888</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>25384</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36633</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>60,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>48486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63678</t>
+          <t>63890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51228</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>43429</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>51228</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19552</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13604</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25344</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>39,15%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>50,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>20818</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>15524</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26700</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15128</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>26558</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>40,99%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>52,58%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19552</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14085</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25800</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>39,15%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>31781</t>
+          <t>32730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48693</t>
+          <t>49893</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>49,53%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30389</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>24597</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>36337</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>60,85%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>49,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>72,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>29966</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24084</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>35260</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24226</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35656</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>59,01%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,42%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>69,43%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30389</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>24141</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>35856</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>60,85%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>52032</t>
+          <t>50832</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68944</t>
+          <t>67995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>67,51%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>50784</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>49941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>75199</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>64263</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>86818</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>45,05%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>78711</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>67251</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>90680</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>66003</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>88793</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>41,95%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,33%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>75199</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>64064</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>87054</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138640</t>
+          <t>137731</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>172841</t>
+          <t>170864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117511</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>105892</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>128447</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,98%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>54,95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>108926</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>96957</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>120386</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>98844</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121634</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>58,05%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>51,67%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>64,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>117511</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>105656</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>128646</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>60,98%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>207506</t>
+          <t>209483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241707</t>
+          <t>242616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>192710</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>192710</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>192710</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>187637</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>187637</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>187637</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>192710</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>192710</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>192710</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6634</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3499</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11228</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,71%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11823</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7169</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15923</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7715</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16979</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>36,87%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6634</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11672</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>23,71%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>13026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24309</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21345</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16751</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24480</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,29%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,87%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>87,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20241</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16141</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24895</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15085</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24349</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>63,13%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>50,34%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,64%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21345</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16307</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>24876</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>76,29%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35734</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47333</t>
+          <t>47017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>27979</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>27979</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>27979</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>32064</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>27979</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>27979</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>27979</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19969</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14398</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25667</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>40,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>28,93%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>51,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>18997</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13847</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25048</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13590</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>25035</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>35,56%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>25,92%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19969</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14511</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>25765</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>40,13%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31559</t>
+          <t>31356</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47529</t>
+          <t>46405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>44,98%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29792</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24094</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35363</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>59,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>48,42%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>71,07%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>34421</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28370</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39571</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>28383</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>39828</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>64,44%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>53,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>74,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>29792</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>23996</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35250</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>59,87%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>55650</t>
+          <t>56774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>71823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>49761</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53418</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>49761</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14366</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10076</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19086</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,38%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>31,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,95%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>14015</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9413</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18218</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>9715</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18403</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>41,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>53,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>14366</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>9653</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19069</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,38%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22198</t>
+          <t>22458</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>34852</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18008</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13288</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>22298</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55,62%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>68,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>19933</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15730</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>24535</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>15545</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>24233</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>58,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18008</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13305</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>22721</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>55,62%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32086</t>
+          <t>31471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44125</t>
+          <t>43865</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>33948</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13184</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18020</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>48,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>18336</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13145</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24407</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12766</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>23857</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>41,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>13184</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>8454</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18363</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>35,37%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24760</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39425</t>
+          <t>39456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -5764,67 +5764,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>24086</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19250</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>28658</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>64,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>76,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>25494</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19423</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30685</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>19973</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>31064</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>58,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>24086</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>18907</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>28816</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>64,63%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41675</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56340</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>37270</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>43830</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>43830</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>43830</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>37270</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>54153</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>45123</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>65094</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,62%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>63172</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>53029</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73357</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>54080</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>73578</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,93%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>54153</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>44835</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>63534</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>104113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>131952</t>
+          <t>131183</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>93232</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>82291</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>102262</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>55,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,38%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>100087</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>89902</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>110230</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>89681</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>109179</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>61,31%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>55,07%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>93232</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>83851</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>102550</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>63,26%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>178693</t>
+          <t>179462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>207254</t>
+          <t>206532</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>147385</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>147385</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>147385</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>163259</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>163259</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>163259</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>147385</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>147385</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>147385</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7248</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3891</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11294</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10452</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6974</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14512</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>40,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>17374</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19892</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>10782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>32605</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29655</t>
+          <t>26521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40818</t>
+          <t>37779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>74,18%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>26308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>50929</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26400</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19676</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32721</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>46,76%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18045</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10682</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23863</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>40,79%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,14%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>53,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29501</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>11114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36150</t>
+          <t>21124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47547</t>
+          <t>42057</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37589</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57301</t>
+          <t>50354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30058</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23737</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>36782</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>53,24%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>42,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>65,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>26197</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20379</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>33560</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>59,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>46,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>34308</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41919</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>60504</t>
+          <t>50537</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>50750</t>
+          <t>42240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>70462</t>
+          <t>58626</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44242</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36136</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108051</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23200</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15833</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>29589</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>28899</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9903</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48174</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>37,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>62,51%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>28896</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19199</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34248</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27563</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74195</t>
+          <t>62917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29155</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22766</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36522</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>69,76%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>48172</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28897</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67168</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>62,5%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30263</t>
+          <t>21930</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22675</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37724</t>
+          <t>29275</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>78435</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59799</t>
+          <t>40264</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106431</t>
+          <t>60788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15694</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11276</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20431</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>49,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>35,78%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>64,83%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14120</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9676</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18738</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>46,2%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,66%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>61,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>14015</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11104</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>29709</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23542</t>
+          <t>23380</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37348</t>
+          <t>35957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,72%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>15823</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11823</t>
+          <t>11086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>34083</t>
+          <t>31531</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27022</t>
+          <t>25283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40828</t>
+          <t>37860</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>61,82%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>72542</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>61711</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>84667</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>71517</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43856</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>89860</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>40,24%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>80096</t>
+          <t>69644</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67131</t>
+          <t>60145</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>91778</t>
+          <t>80004</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>151613</t>
+          <t>142186</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113536</t>
+          <t>128241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171925</t>
+          <t>156954</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>50,97%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>92410</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>80285</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>103241</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>56,02%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>62,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>106198</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>87855</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>133859</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>59,76%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,44%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>75,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>102105</t>
+          <t>73348</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>90423</t>
+          <t>62988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115070</t>
+          <t>82847</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>208303</t>
+          <t>165758</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>187991</t>
+          <t>150990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246380</t>
+          <t>179703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
